--- a/Docs/mohio-language-reference-v3.6.xlsx
+++ b/Docs/mohio-language-reference-v3.6.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foundation Blocks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verbs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoQL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expressions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="String Operations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pattern Blocks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiers &amp; Prefixes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Primitives" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mio Services" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error Reference" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shapes &amp; Types" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired &amp; Candidates" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Foundation Blocks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Verbs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MoQL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Expressions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="String Operations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pattern Blocks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Modifiers &amp; Prefixes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AI Primitives" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Mio Services" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Error Reference" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Shapes &amp; Types" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Retired &amp; Candidates" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="42" min="1" max="1"/>
@@ -1012,9 +1012,12 @@
       </c>
       <c r="D6" s="46" t="inlineStr">
         <is>
-          <t>saga process_order(order)
-    step charge
-    step reserve
+          <t>saga process_order
+    step charge_card
+        // ...
+        compensate
+            // undo
+        step: done
 saga: done</t>
         </is>
       </c>
@@ -1032,7 +1035,7 @@
       </c>
       <c r="C7" s="46" t="inlineStr">
         <is>
-          <t>Data structure contract — simultaneously DB schema, API format, frontend validation, compliance enforcement, and UI generation. One declaration, everything reads from it.</t>
+          <t>Describes a data element. Declares; does not run. Data structure contract — simultaneously DB schema, API format, frontend validation, compliance enforcement, and UI generation. One declaration, everything reads from it.</t>
         </is>
       </c>
       <c r="D7" s="46" t="inlineStr">
@@ -1048,20 +1051,45 @@
     <row r="8" ht="72" customHeight="1" s="42">
       <c r="A8" s="46" t="inlineStr">
         <is>
+          <t>task [Name]</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Action contract</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>The callable action-doer. Declares logic; runs when `call`ed. Reusable logic — inputs via `take`, invoked with `call`, optionally returns a value with `give back`.</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>task SendWelcome
+    take member as sh.Member
+    // send email
+task: done</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1" s="42">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
           <t>pattern [Name]</t>
         </is>
       </c>
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Text contract</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Named text pattern for validation, extraction, and replacement. Declared once, used anywhere.</t>
         </is>
       </c>
-      <c r="D8" s="46" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>pattern Email
     any characters as local_part
@@ -1071,23 +1099,23 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1" s="42">
-      <c r="A9" s="46" t="inlineStr">
+    <row r="10" ht="72" customHeight="1" s="42">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>miomap [Name]</t>
         </is>
       </c>
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Transform contract</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>Field mapping between two shapes. Transformation contract — connector data to canonical shape.</t>
         </is>
       </c>
-      <c r="D9" s="46" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>miomap StripeToInvoice
     translate sh.StripeCharge to sh.Invoice
@@ -1096,46 +1124,46 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1" s="42">
-      <c r="A10" s="46" t="inlineStr">
+    <row r="11" ht="72" customHeight="1" s="42">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>connect [name] as [type]</t>
         </is>
       </c>
-      <c r="B10" s="46" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Connection</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>Declare a named database or cache connection. Credentials always via env. or secret.</t>
         </is>
       </c>
-      <c r="D10" s="46" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>connect db as postgres from env.DATABASE_URL
 connect cache as redis from env.REDIS_URL</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1" s="42">
-      <c r="A11" s="46" t="inlineStr">
+    <row r="12" ht="72" customHeight="1" s="42">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>mioconnect [Name]</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Service connector</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>Named external service connector. Intent verbs (find, retrieve, save) work against it.</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>mioconnect Stripe
     identify with secret.STRIPE_KEY
@@ -1143,46 +1171,46 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1" s="42">
-      <c r="A12" s="46" t="inlineStr">
+    <row r="13" ht="72" customHeight="1" s="42">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>sector:</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>Profile activation</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Activates a sector profile — compliance frameworks, field type awareness, AI constraints, retention rules, breach notification defaults.</t>
         </is>
       </c>
-      <c r="D12" s="46" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>sector: financial
 sector: healthcare</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1" s="42">
-      <c r="A13" s="46" t="inlineStr">
+    <row r="14" ht="72" customHeight="1" s="42">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>compliance:</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Framework activation</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Activates a specific compliance framework runtime. sector: activates multiple; compliance: activates one explicitly.</t>
         </is>
       </c>
-      <c r="D13" s="46" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>compliance: HIPAA
 compliance: PCI_DSS
@@ -1190,46 +1218,46 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="72" customHeight="1" s="42">
-      <c r="A14" s="46" t="inlineStr">
+    <row r="15" ht="72" customHeight="1" s="42">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>include "[file]"</t>
         </is>
       </c>
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>Pull another .mho file inline. Used for shared foundation files, patterns, shapes.</t>
         </is>
       </c>
-      <c r="D14" s="46" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>include "config/app.mho"
 include "patterns/patterns.mho"</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="72" customHeight="1" s="42">
-      <c r="A15" s="46" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>timespan [Name]</t>
         </is>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Time context</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>Named time context block. Activates its own vocabulary: precision, exclusions, business days. Not a data type — a logic universe.</t>
         </is>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>timespan last_quarter
     from 90 days ago
@@ -4372,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="47" min="1" max="1"/>
@@ -5156,9 +5184,9 @@
       </c>
     </row>
     <row r="35" ht="55.5" customHeight="1" s="42">
-      <c r="A35" s="54" t="inlineStr">
-        <is>
-          <t>task [Name](params)</t>
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>page [path] from [file]</t>
         </is>
       </c>
       <c r="B35" s="66" t="inlineStr">
@@ -5166,23 +5194,21 @@
           <t>Declaration</t>
         </is>
       </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>Named reusable block of logic.</t>
-        </is>
-      </c>
-      <c r="D35" s="56" t="inlineStr">
-        <is>
-          <t>task SendWelcome(member as sh.Member)
-    // send email
-SendWelcome: done</t>
+      <c r="C35" s="62" t="inlineStr">
+        <is>
+          <t>Declares a URL route to a page file.</t>
+        </is>
+      </c>
+      <c r="D35" s="52" t="inlineStr">
+        <is>
+          <t>page /dashboard from pages/dashboard.mho</t>
         </is>
       </c>
     </row>
     <row r="36" ht="55.5" customHeight="1" s="42">
-      <c r="A36" s="50" t="inlineStr">
-        <is>
-          <t>page [path] from [file]</t>
+      <c r="A36" s="54" t="inlineStr">
+        <is>
+          <t>section [path]</t>
         </is>
       </c>
       <c r="B36" s="66" t="inlineStr">
@@ -5190,34 +5216,12 @@
           <t>Declaration</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
-        <is>
-          <t>Declares a URL route to a page file.</t>
-        </is>
-      </c>
-      <c r="D36" s="52" t="inlineStr">
-        <is>
-          <t>page /dashboard from pages/dashboard.mho</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="55.5" customHeight="1" s="42">
-      <c r="A37" s="54" t="inlineStr">
-        <is>
-          <t>section [path]</t>
-        </is>
-      </c>
-      <c r="B37" s="66" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
+      <c r="C36" s="64" t="inlineStr">
         <is>
           <t>Grouped pages with shared auth rules.</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
+      <c r="D36" s="56" t="inlineStr">
         <is>
           <t>section /admin
     require role admin
@@ -5226,23 +5230,23 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="55.5" customHeight="1" s="42">
-      <c r="A38" s="50" t="inlineStr">
+    <row r="37" ht="55.5" customHeight="1" s="42">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>connect [name] as [type]</t>
         </is>
       </c>
-      <c r="B38" s="66" t="inlineStr">
+      <c r="B37" s="66" t="inlineStr">
         <is>
           <t>Declaration</t>
         </is>
       </c>
-      <c r="C38" s="62" t="inlineStr">
+      <c r="C37" s="62" t="inlineStr">
         <is>
           <t>Declare a named database or external connection.</t>
         </is>
       </c>
-      <c r="D38" s="52" t="inlineStr">
+      <c r="D37" s="52" t="inlineStr">
         <is>
           <t>connect db as postgres
     from env.DATABASE_URL
@@ -5250,23 +5254,23 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="55.5" customHeight="1" s="42">
-      <c r="A39" s="54" t="inlineStr">
+    <row r="38" ht="55.5" customHeight="1" s="42">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>mioconnect [Name]</t>
         </is>
       </c>
-      <c r="B39" s="66" t="inlineStr">
+      <c r="B38" s="66" t="inlineStr">
         <is>
           <t>Declaration</t>
         </is>
       </c>
-      <c r="C39" s="64" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>Declare a named external service connector.</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
+      <c r="D38" s="56" t="inlineStr">
         <is>
           <t>mioconnect Stripe
     identify with secret.STRIPE_KEY
@@ -5274,55 +5278,55 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="55.5" customHeight="1" s="42">
+      <c r="A39" s="50" t="inlineStr">
+        <is>
+          <t>include [file]</t>
+        </is>
+      </c>
+      <c r="B39" s="66" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="C39" s="62" t="inlineStr">
+        <is>
+          <t>Pull in another .mho file inline.</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>include "config/app.mho"</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="55.5" customHeight="1" s="42">
-      <c r="A40" s="50" t="inlineStr">
-        <is>
-          <t>include [file]</t>
-        </is>
-      </c>
-      <c r="B40" s="66" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="C40" s="62" t="inlineStr">
-        <is>
-          <t>Pull in another .mho file inline.</t>
-        </is>
-      </c>
-      <c r="D40" s="52" t="inlineStr">
-        <is>
-          <t>include "config/app.mho"</t>
-        </is>
-      </c>
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OUTPUT</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="n"/>
+      <c r="C40" s="59" t="n"/>
+      <c r="D40" s="60" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="42">
-      <c r="A41" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OUTPUT</t>
-        </is>
-      </c>
-      <c r="B41" s="59" t="n"/>
-      <c r="C41" s="59" t="n"/>
-      <c r="D41" s="60" t="n"/>
-    </row>
-    <row r="42" ht="55.5" customHeight="1" s="42">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>give back</t>
         </is>
       </c>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C42" s="62" t="inlineStr">
+      <c r="C41" s="62" t="inlineStr">
         <is>
           <t>Return a value and exit the current block. Universal return.</t>
         </is>
       </c>
-      <c r="D42" s="52" t="inlineStr">
+      <c r="D41" s="52" t="inlineStr">
         <is>
           <t>give back member as json
 give back 404 "Not found"
@@ -5330,45 +5334,45 @@
         </is>
       </c>
     </row>
+    <row r="42" ht="55.5" customHeight="1" s="42">
+      <c r="A42" s="54" t="inlineStr">
+        <is>
+          <t>send [data] to [session]</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="C42" s="64" t="inlineStr">
+        <is>
+          <t>Push data to a WebSocket or SSE session.</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t>send board_state to member.session</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="55.5" customHeight="1" s="42">
-      <c r="A43" s="54" t="inlineStr">
-        <is>
-          <t>send [data] to [session]</t>
-        </is>
-      </c>
-      <c r="B43" s="63" t="inlineStr">
+      <c r="A43" s="50" t="inlineStr">
+        <is>
+          <t>broadcast to room [name]</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C43" s="64" t="inlineStr">
-        <is>
-          <t>Push data to a WebSocket or SSE session.</t>
-        </is>
-      </c>
-      <c r="D43" s="56" t="inlineStr">
-        <is>
-          <t>send board_state to member.session</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="55.5" customHeight="1" s="42">
-      <c r="A44" s="50" t="inlineStr">
-        <is>
-          <t>broadcast to room [name]</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="C44" s="62" t="inlineStr">
+      <c r="C43" s="62" t="inlineStr">
         <is>
           <t>Send to all connections in a room.</t>
         </is>
       </c>
-      <c r="D44" s="52" t="inlineStr">
+      <c r="D43" s="52" t="inlineStr">
         <is>
           <t>broadcast to room "board-{{ id }}"
     except member.session
@@ -5376,23 +5380,23 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="55.5" customHeight="1" s="42">
-      <c r="A45" s="54" t="inlineStr">
+    <row r="44" ht="55.5" customHeight="1" s="42">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>stream [data] to [session]</t>
         </is>
       </c>
-      <c r="B45" s="63" t="inlineStr">
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C44" s="64" t="inlineStr">
         <is>
           <t>Start an SSE or file stream to a session.</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
+      <c r="D44" s="56" t="inlineStr">
         <is>
           <t>stream dashboard_stats to member.session
     live true
@@ -5403,23 +5407,23 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="55.5" customHeight="1" s="42">
-      <c r="A46" s="50" t="inlineStr">
+    <row r="45" ht="55.5" customHeight="1" s="42">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>stream manifest [name]</t>
         </is>
       </c>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C46" s="62" t="inlineStr">
+      <c r="C45" s="62" t="inlineStr">
         <is>
           <t>Serve HLS manifest for audio/video streaming.</t>
         </is>
       </c>
-      <c r="D46" s="52" t="inlineStr">
+      <c r="D45" s="52" t="inlineStr">
         <is>
           <t>stream manifest episode_stream
     for episode.id
@@ -5429,23 +5433,23 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="55.5" customHeight="1" s="42">
-      <c r="A47" s="54" t="inlineStr">
+    <row r="46" ht="55.5" customHeight="1" s="42">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>show</t>
         </is>
       </c>
-      <c r="B47" s="63" t="inlineStr">
+      <c r="B46" s="63" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="C47" s="64" t="inlineStr">
+      <c r="C46" s="64" t="inlineStr">
         <is>
           <t>Render HTML to the response.</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
+      <c r="D46" s="56" t="inlineStr">
         <is>
           <t>show
     &lt;h1&gt;Welcome, {{ member.name }}&lt;/h1&gt;
@@ -5453,101 +5457,101 @@
         </is>
       </c>
     </row>
+    <row r="47" ht="55.5" customHeight="1" s="42">
+      <c r="A47" s="50" t="inlineStr">
+        <is>
+          <t>jump to [path]</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C47" s="62" t="inlineStr">
+        <is>
+          <t>Client-side navigation / redirect.</t>
+        </is>
+      </c>
+      <c r="D47" s="52" t="inlineStr">
+        <is>
+          <t>jump to /dashboard</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="55.5" customHeight="1" s="42">
-      <c r="A48" s="50" t="inlineStr">
-        <is>
-          <t>jump to [path]</t>
-        </is>
-      </c>
-      <c r="B48" s="61" t="inlineStr">
+      <c r="A48" s="54" t="inlineStr">
+        <is>
+          <t>close stream</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C48" s="62" t="inlineStr">
-        <is>
-          <t>Client-side navigation / redirect.</t>
-        </is>
-      </c>
-      <c r="D48" s="52" t="inlineStr">
-        <is>
-          <t>jump to /dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="55.5" customHeight="1" s="42">
-      <c r="A49" s="54" t="inlineStr">
-        <is>
-          <t>close stream</t>
-        </is>
-      </c>
-      <c r="B49" s="63" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C49" s="64" t="inlineStr">
+      <c r="C48" s="64" t="inlineStr">
         <is>
           <t>Finalize and close an active stream.</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
+      <c r="D48" s="56" t="inlineStr">
         <is>
           <t>on complete
     close stream</t>
         </is>
       </c>
     </row>
+    <row r="49" ht="55.5" customHeight="1" s="42">
+      <c r="A49" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AUTH &amp; ACCESS</t>
+        </is>
+      </c>
+      <c r="B49" s="59" t="n"/>
+      <c r="C49" s="59" t="n"/>
+      <c r="D49" s="60" t="n"/>
+    </row>
     <row r="50" ht="15.75" customHeight="1" s="42">
-      <c r="A50" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AUTH &amp; ACCESS</t>
-        </is>
-      </c>
-      <c r="B50" s="59" t="n"/>
-      <c r="C50" s="59" t="n"/>
-      <c r="D50" s="60" t="n"/>
-    </row>
-    <row r="51" ht="55.5" customHeight="1" s="42">
-      <c r="A51" s="54" t="inlineStr">
+      <c r="A50" s="54" t="inlineStr">
         <is>
           <t>require role [name]</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B50" s="66" t="inlineStr">
         <is>
           <t>Declaration</t>
         </is>
       </c>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="C50" s="64" t="inlineStr">
         <is>
           <t>Access gate — compiler verifies role names match declarations.</t>
         </is>
       </c>
-      <c r="D51" s="56" t="inlineStr">
+      <c r="D50" s="56" t="inlineStr">
         <is>
           <t>require role admin or editor
 require role not banned</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="55.5" customHeight="1" s="42">
-      <c r="A52" s="50" t="inlineStr">
+    <row r="51" ht="55.5" customHeight="1" s="42">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>verify token from [source]</t>
         </is>
       </c>
-      <c r="B52" s="61" t="inlineStr">
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C52" s="62" t="inlineStr">
+      <c r="C51" s="62" t="inlineStr">
         <is>
           <t>Validate a signed token, check scope.</t>
         </is>
       </c>
-      <c r="D52" s="52" t="inlineStr">
+      <c r="D51" s="52" t="inlineStr">
         <is>
           <t>verify token from request.query.token
     scope "download:invoice-*"
@@ -5556,23 +5560,23 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="55.5" customHeight="1" s="42">
-      <c r="A53" s="54" t="inlineStr">
+    <row r="52" ht="55.5" customHeight="1" s="42">
+      <c r="A52" s="54" t="inlineStr">
         <is>
           <t>sign url for [storage]</t>
         </is>
       </c>
-      <c r="B53" s="63" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C53" s="64" t="inlineStr">
+      <c r="C52" s="64" t="inlineStr">
         <is>
           <t>Generate a signed URL for temporary file access.</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
+      <c r="D52" s="56" t="inlineStr">
         <is>
           <t>sign url for cloud_storage/file.pdf
     expires in 15 minutes
@@ -5581,23 +5585,23 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="55.5" customHeight="1" s="42">
-      <c r="A54" s="50" t="inlineStr">
+    <row r="53" ht="55.5" customHeight="1" s="42">
+      <c r="A53" s="50" t="inlineStr">
         <is>
           <t>sign upload url for [storage]</t>
         </is>
       </c>
-      <c r="B54" s="61" t="inlineStr">
+      <c r="B53" s="61" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C54" s="62" t="inlineStr">
+      <c r="C53" s="62" t="inlineStr">
         <is>
           <t>Generate a signed URL for direct client upload.</t>
         </is>
       </c>
-      <c r="D54" s="52" t="inlineStr">
+      <c r="D53" s="52" t="inlineStr">
         <is>
           <t>sign upload url for cloud_storage
     expires in 1 hour
@@ -5606,33 +5610,33 @@
         </is>
       </c>
     </row>
+    <row r="54" ht="55.5" customHeight="1" s="42">
+      <c r="A54" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AI PRIMITIVES</t>
+        </is>
+      </c>
+      <c r="B54" s="59" t="n"/>
+      <c r="C54" s="59" t="n"/>
+      <c r="D54" s="60" t="n"/>
+    </row>
     <row r="55" ht="15.75" customHeight="1" s="42">
-      <c r="A55" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AI PRIMITIVES</t>
-        </is>
-      </c>
-      <c r="B55" s="59" t="n"/>
-      <c r="C55" s="59" t="n"/>
-      <c r="D55" s="60" t="n"/>
-    </row>
-    <row r="56" ht="55.5" customHeight="1" s="42">
-      <c r="A56" s="50" t="inlineStr">
+      <c r="A55" s="50" t="inlineStr">
         <is>
           <t>ai.decide [name] returns [type]</t>
         </is>
       </c>
-      <c r="B56" s="65" t="inlineStr">
+      <c r="B55" s="65" t="inlineStr">
         <is>
           <t>AI-Native (hard reserved)</t>
         </is>
       </c>
-      <c r="C56" s="62" t="inlineStr">
+      <c r="C55" s="62" t="inlineStr">
         <is>
           <t>AI reasoning block. Typed return, confidence threshold, mandatory fallback, automatic audit. Compiler refuses to build without fallback.</t>
         </is>
       </c>
-      <c r="D56" s="52" t="inlineStr">
+      <c r="D55" s="52" t="inlineStr">
         <is>
           <t>ai.decide isFraudulent(tx) returns boolean
     check confidence above 0.85
@@ -5644,46 +5648,46 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="55.5" customHeight="1" s="42">
-      <c r="A57" s="54" t="inlineStr">
+    <row r="56" ht="55.5" customHeight="1" s="42">
+      <c r="A56" s="54" t="inlineStr">
         <is>
           <t>not confident</t>
         </is>
       </c>
-      <c r="B57" s="89" t="inlineStr">
+      <c r="B56" s="89" t="inlineStr">
         <is>
           <t>AI-Native</t>
         </is>
       </c>
-      <c r="C57" s="64" t="inlineStr">
+      <c r="C56" s="64" t="inlineStr">
         <is>
           <t>Two-line fallback pattern inside ai.decide. Fires when confidence is below threshold.</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
+      <c r="D56" s="56" t="inlineStr">
         <is>
           <t>not confident
     give back pending "Manual review required"</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="55.5" customHeight="1" s="42">
-      <c r="A58" s="50" t="inlineStr">
+    <row r="57" ht="55.5" customHeight="1" s="42">
+      <c r="A57" s="50" t="inlineStr">
         <is>
           <t>ai.explain</t>
         </is>
       </c>
-      <c r="B58" s="65" t="inlineStr">
+      <c r="B57" s="65" t="inlineStr">
         <is>
           <t>AI-Native (hard reserved)</t>
         </is>
       </c>
-      <c r="C58" s="62" t="inlineStr">
+      <c r="C57" s="62" t="inlineStr">
         <is>
           <t>Generate plain-language explanation of an ai.decide result. Audience and format specified.</t>
         </is>
       </c>
-      <c r="D58" s="52" t="inlineStr">
+      <c r="D57" s="52" t="inlineStr">
         <is>
           <t>ai.explain decision loan_approval
     audience "applicant"
@@ -5691,45 +5695,45 @@
         </is>
       </c>
     </row>
+    <row r="58" ht="55.5" customHeight="1" s="42">
+      <c r="A58" s="54" t="inlineStr">
+        <is>
+          <t>ai.audit</t>
+        </is>
+      </c>
+      <c r="B58" s="65" t="inlineStr">
+        <is>
+          <t>AI-Native (hard reserved)</t>
+        </is>
+      </c>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
+          <t>Permanent immutable decision record — inputs, outputs, confidence, model, timestamp.</t>
+        </is>
+      </c>
+      <c r="D58" s="56" t="inlineStr">
+        <is>
+          <t>ai.audit to compliance_log</t>
+        </is>
+      </c>
+    </row>
     <row r="59" ht="55.5" customHeight="1" s="42">
-      <c r="A59" s="54" t="inlineStr">
-        <is>
-          <t>ai.audit</t>
-        </is>
-      </c>
-      <c r="B59" s="65" t="inlineStr">
-        <is>
-          <t>AI-Native (hard reserved)</t>
-        </is>
-      </c>
-      <c r="C59" s="64" t="inlineStr">
-        <is>
-          <t>Permanent immutable decision record — inputs, outputs, confidence, model, timestamp.</t>
-        </is>
-      </c>
-      <c r="D59" s="56" t="inlineStr">
-        <is>
-          <t>ai.audit to compliance_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="55.5" customHeight="1" s="42">
-      <c r="A60" s="50" t="inlineStr">
+      <c r="A59" s="50" t="inlineStr">
         <is>
           <t>ai.create image/audio/logic/text</t>
         </is>
       </c>
-      <c r="B60" s="89" t="inlineStr">
+      <c r="B59" s="89" t="inlineStr">
         <is>
           <t>AI-Native</t>
         </is>
       </c>
-      <c r="C60" s="62" t="inlineStr">
+      <c r="C59" s="62" t="inlineStr">
         <is>
           <t>Generate content inline using AI. Four type modifiers.</t>
         </is>
       </c>
-      <c r="D60" s="52" t="inlineStr">
+      <c r="D59" s="52" t="inlineStr">
         <is>
           <t>ai.create text
     prompt "Write subject line for {{ member.name }}"
@@ -5737,23 +5741,23 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="55.5" customHeight="1" s="42">
-      <c r="A61" s="54" t="inlineStr">
+    <row r="60" ht="55.5" customHeight="1" s="42">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>mioai.generate</t>
         </is>
       </c>
-      <c r="B61" s="67" t="inlineStr">
+      <c r="B60" s="67" t="inlineStr">
         <is>
           <t>Built-in</t>
         </is>
       </c>
-      <c r="C61" s="64" t="inlineStr">
+      <c r="C60" s="64" t="inlineStr">
         <is>
           <t>AI text/content generation with streaming. Full attribute set.</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
+      <c r="D60" s="56" t="inlineStr">
         <is>
           <t>mioai.generate text
     prompt request.question
@@ -5765,120 +5769,121 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="55.5" customHeight="1" s="42">
-      <c r="A62" s="50" t="inlineStr">
+    <row r="61" ht="55.5" customHeight="1" s="42">
+      <c r="A61" s="50" t="inlineStr">
         <is>
           <t>force confidence [n]</t>
         </is>
       </c>
-      <c r="B62" s="90" t="inlineStr">
+      <c r="B61" s="90" t="inlineStr">
         <is>
           <t>Test-only</t>
         </is>
       </c>
-      <c r="C62" s="62" t="inlineStr">
+      <c r="C61" s="62" t="inlineStr">
         <is>
           <t>Override AI confidence score. Valid inside miotest it blocks only.</t>
         </is>
       </c>
-      <c r="D62" s="52" t="inlineStr">
+      <c r="D61" s="52" t="inlineStr">
         <is>
           <t>force confidence 0.55
 // forces fallback path</t>
         </is>
       </c>
     </row>
+    <row r="62" ht="55.5" customHeight="1" s="42">
+      <c r="A62" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SAGAS &amp; TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="B62" s="59" t="n"/>
+      <c r="C62" s="59" t="n"/>
+      <c r="D62" s="60" t="n"/>
+    </row>
     <row r="63" ht="15.75" customHeight="1" s="42">
-      <c r="A63" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SAGAS &amp; TRANSACTIONS</t>
-        </is>
-      </c>
-      <c r="B63" s="59" t="n"/>
-      <c r="C63" s="59" t="n"/>
-      <c r="D63" s="60" t="n"/>
-    </row>
-    <row r="64" ht="55.5" customHeight="1" s="42">
-      <c r="A64" s="50" t="inlineStr">
+      <c r="A63" s="50" t="inlineStr">
         <is>
           <t>saga [name]</t>
         </is>
       </c>
-      <c r="B64" s="61" t="inlineStr">
+      <c r="B63" s="61" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="C64" s="62" t="inlineStr">
+      <c r="C63" s="62" t="inlineStr">
         <is>
           <t>Distributed transaction with named rollback steps. The code is the policy.</t>
         </is>
       </c>
-      <c r="D64" s="52" t="inlineStr">
-        <is>
-          <t>saga process_order(order, payment)
+      <c r="D63" s="52" t="inlineStr">
+        <is>
+          <t>saga process_order
     step charge_card
         // ...
-        on.rollback refund stripe.charge
+        compensate
+            refund stripe.charge
     step: done
 saga: done</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="55.5" customHeight="1" s="42">
-      <c r="A65" s="54" t="inlineStr">
+    <row r="64" ht="55.5" customHeight="1" s="42">
+      <c r="A64" s="54" t="inlineStr">
         <is>
           <t>step [name]</t>
         </is>
       </c>
-      <c r="B65" s="63" t="inlineStr">
+      <c r="B64" s="63" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="C65" s="64" t="inlineStr">
+      <c r="C64" s="64" t="inlineStr">
         <is>
           <t>Named step inside a saga. Closer: step: done.</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
+      <c r="D64" s="56" t="inlineStr">
         <is>
           <t>step reserve_inventory
     // ...
-    on.rollback
+    compensate
         update warehouse.inventory
             status available
     step: done</t>
         </is>
       </c>
     </row>
+    <row r="65" ht="55.5" customHeight="1" s="42">
+      <c r="A65" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ERROR HANDLING</t>
+        </is>
+      </c>
+      <c r="B65" s="59" t="n"/>
+      <c r="C65" s="59" t="n"/>
+      <c r="D65" s="60" t="n"/>
+    </row>
     <row r="66" ht="15.75" customHeight="1" s="42">
-      <c r="A66" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ERROR HANDLING</t>
-        </is>
-      </c>
-      <c r="B66" s="59" t="n"/>
-      <c r="C66" s="59" t="n"/>
-      <c r="D66" s="60" t="n"/>
-    </row>
-    <row r="67" ht="55.5" customHeight="1" s="42">
-      <c r="A67" s="54" t="inlineStr">
+      <c r="A66" s="54" t="inlineStr">
         <is>
           <t>on.success</t>
         </is>
       </c>
-      <c r="B67" s="63" t="inlineStr">
+      <c r="B66" s="63" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="C67" s="64" t="inlineStr">
+      <c r="C66" s="64" t="inlineStr">
         <is>
           <t>Handler when a block completes successfully.</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
+      <c r="D66" s="56" t="inlineStr">
         <is>
           <t>mioauth.login
     on.success jump to /dashboard
@@ -5886,23 +5891,23 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="55.5" customHeight="1" s="42">
-      <c r="A68" s="50" t="inlineStr">
+    <row r="67" ht="55.5" customHeight="1" s="42">
+      <c r="A67" s="50" t="inlineStr">
         <is>
           <t>on.failure</t>
         </is>
       </c>
-      <c r="B68" s="61" t="inlineStr">
+      <c r="B67" s="61" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="C68" s="62" t="inlineStr">
+      <c r="C67" s="62" t="inlineStr">
         <is>
           <t>Handler when a block fails. Exits the block — no further execution.</t>
         </is>
       </c>
-      <c r="D68" s="52" t="inlineStr">
+      <c r="D67" s="52" t="inlineStr">
         <is>
           <t>retrieve member in db.members
     on.failure give back 404 "Not found"
@@ -5910,46 +5915,46 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="55.5" customHeight="1" s="42">
-      <c r="A69" s="54" t="inlineStr">
+    <row r="68" ht="55.5" customHeight="1" s="42">
+      <c r="A68" s="54" t="inlineStr">
         <is>
           <t>raise "[message]"</t>
         </is>
       </c>
-      <c r="B69" s="63" t="inlineStr">
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C69" s="64" t="inlineStr">
+      <c r="C68" s="64" t="inlineStr">
         <is>
           <t>Throw a named error that can be caught upstream.</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
+      <c r="D68" s="56" t="inlineStr">
         <is>
           <t>if not card.valid
     raise "Card declined"</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="55.5" customHeight="1" s="42">
-      <c r="A70" s="50" t="inlineStr">
+    <row r="69" ht="55.5" customHeight="1" s="42">
+      <c r="A69" s="50" t="inlineStr">
         <is>
           <t>raise again</t>
         </is>
       </c>
-      <c r="B70" s="61" t="inlineStr">
+      <c r="B69" s="61" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C70" s="62" t="inlineStr">
+      <c r="C69" s="62" t="inlineStr">
         <is>
           <t>Re-throw a caught error up the call stack.</t>
         </is>
       </c>
-      <c r="D70" s="52" t="inlineStr">
+      <c r="D69" s="52" t="inlineStr">
         <is>
           <t>catch any as err
     miolog.app_log.error err.message done
@@ -5957,17 +5962,18 @@
         </is>
       </c>
     </row>
+    <row r="70" ht="55.5" customHeight="1" s="42"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A49:D49"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
